--- a/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
+++ b/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
@@ -1368,12 +1368,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>75–77</t>
+          <t>75–76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>نعم — راجع تقرير التكرارات</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>78–78</t>
+          <t>77–108</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 2، فُتات أسطر: 17</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 2؛ فُتات أسطر: 17</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>79–82</t>
+          <t>109–112</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>83–83</t>
+          <t>113–113</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>84–84</t>
+          <t>114–114</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>85–85</t>
+          <t>115–115</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>86–86</t>
+          <t>116–116</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>87–122</t>
+          <t>117–152</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>123–140</t>
+          <t>153–170</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>141–141</t>
+          <t>171–171</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>142–144</t>
+          <t>172–174</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>145–148</t>
+          <t>175–178</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>149–149</t>
+          <t>179–179</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>150–154</t>
+          <t>180–181</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>155–156</t>
+          <t>182–183</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 2</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>تكرار حروف: 1</t>
+          <t>تكرار حروف: 2</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>157–157</t>
+          <t>184–185</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 7</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 7</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>158–160</t>
+          <t>186–188</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>161–161</t>
+          <t>189–189</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>162–170</t>
+          <t>190–198</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>171–176</t>
+          <t>199–204</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>177–225</t>
+          <t>205–253</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>226–228</t>
+          <t>254–256</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>229–232</t>
+          <t>257–260</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>233–234</t>
+          <t>261–262</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>235–235</t>
+          <t>263–263</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>236–238</t>
+          <t>264–266</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>239–239</t>
+          <t>267–267</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 7</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 7</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>240–240</t>
+          <t>268–268</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241–257</t>
+          <t>269–285</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>258–260</t>
+          <t>286–288</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>261–263</t>
+          <t>289–291</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 6</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>نعم — راجع تقرير التكرارات</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 6</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>264–265</t>
+          <t>292–293</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>266–266</t>
+          <t>294–294</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>267–267</t>
+          <t>295–295</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>268–268</t>
+          <t>296–296</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>269–269</t>
+          <t>297–297</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>270–279</t>
+          <t>298–307</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>280–280</t>
+          <t>308–308</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>281–283</t>
+          <t>309–311</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>284–288</t>
+          <t>312–316</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>289–289</t>
+          <t>317–317</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>290–290</t>
+          <t>318–318</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>291–326</t>
+          <t>319–354</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>327–328</t>
+          <t>355–356</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>329–338</t>
+          <t>357–366</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>339–343</t>
+          <t>367–371</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>344–348</t>
+          <t>372–376</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>349–353</t>
+          <t>377–381</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>354–360</t>
+          <t>382–388</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>361–361</t>
+          <t>389–389</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>362–367</t>
+          <t>390–395</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>368–368</t>
+          <t>396–396</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>369–369</t>
+          <t>397–397</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>370–370</t>
+          <t>398–398</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>371–371</t>
+          <t>399–399</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>372–375</t>
+          <t>400–403</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>376–376</t>
+          <t>404–404</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>377–378</t>
+          <t>405–406</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>379–379</t>
+          <t>407–407</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>380–384</t>
+          <t>408–418</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 9</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 11، فُتات أسطر: 7</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>تكرار حروف: 9</t>
+          <t>تكرار حروف: 11؛ فُتات أسطر: 7</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ضمن النطاق الواضح</t>
+          <t>يحتاج مراجعة بشرية</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>385–385</t>
+          <t>419–419</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>386–389</t>
+          <t>420–423</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>390–391</t>
+          <t>424–425</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>392–397</t>
+          <t>426–431</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>398–403</t>
+          <t>432–437</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>404–406</t>
+          <t>438–440</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>407–408</t>
+          <t>441–442</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>409–410</t>
+          <t>443–444</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>411–414</t>
+          <t>445–448</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>415–421</t>
+          <t>449–455</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>422–425</t>
+          <t>456–459</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>426–427</t>
+          <t>460–461</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>428–429</t>
+          <t>462–463</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>430–431</t>
+          <t>464–465</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>432–468</t>
+          <t>466–502</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>469–473</t>
+          <t>503–507</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>474–474</t>
+          <t>508–518</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1، فُتات أسطر: 8</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 1؛ فُتات أسطر: 8</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>يحتاج مراجعة بشرية</t>
+          <t>ضمن النطاق الواضح</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>475–478</t>
+          <t>519–522</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>479–486</t>
+          <t>523–530</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>487–492</t>
+          <t>531–536</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>493–498</t>
+          <t>537–542</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>499–500</t>
+          <t>543–544</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>501–502</t>
+          <t>545–546</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>503–507</t>
+          <t>547–551</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>508–509</t>
+          <t>552–553</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>510–511</t>
+          <t>554–555</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>512–514</t>
+          <t>556–558</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>515–517</t>
+          <t>559–561</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>518–520</t>
+          <t>562–564</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>521–523</t>
+          <t>565–567</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>524–526</t>
+          <t>568–570</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>527–529</t>
+          <t>571–573</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>530–532</t>
+          <t>574–576</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>533–535</t>
+          <t>577–579</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>536–538</t>
+          <t>580–582</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>539–541</t>
+          <t>583–585</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>542–545</t>
+          <t>586–589</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>546–549</t>
+          <t>590–593</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>550–554</t>
+          <t>594–598</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>555–559</t>
+          <t>599–603</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>560–561</t>
+          <t>604–605</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>562–572</t>
+          <t>606–616</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>573–586</t>
+          <t>617–630</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>587–592</t>
+          <t>631–636</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>593–595</t>
+          <t>637–639</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>596–601</t>
+          <t>640–645</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>602–602</t>
+          <t>646–646</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>603–605</t>
+          <t>647–649</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>606–606</t>
+          <t>650–650</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>607–608</t>
+          <t>651–652</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>609–614</t>
+          <t>653–658</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>615–615</t>
+          <t>659–659</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>616–616</t>
+          <t>660–660</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>617–617</t>
+          <t>661–661</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>618–618</t>
+          <t>662–662</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>619–669</t>
+          <t>663–713</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>670–703</t>
+          <t>714–747</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>704–743</t>
+          <t>748–787</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>744–767</t>
+          <t>788–811</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>768–872</t>
+          <t>812–916</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>873–873</t>
+          <t>917–917</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>874–874</t>
+          <t>918–918</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>875–891</t>
+          <t>919–935</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>892–903</t>
+          <t>936–947</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>904–915</t>
+          <t>948–959</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>916–923</t>
+          <t>960–967</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>924–951</t>
+          <t>968–995</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>952–952</t>
+          <t>996–996</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>953–953</t>
+          <t>997–997</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>954–971</t>
+          <t>998–1015</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>972–976</t>
+          <t>1016–1020</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>977–985</t>
+          <t>1021–1029</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>986–987</t>
+          <t>1030–1031</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>988–988</t>
+          <t>1032–1032</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>يحتاج مراجعة بشرية</t>
+          <t>ضمن النطاق الواضح</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>989–1081</t>
+          <t>1033–1125</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1082–1083</t>
+          <t>1126–1127</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1084–1092</t>
+          <t>1128–1136</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1093–1127</t>
+          <t>1137–1171</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1128–1163</t>
+          <t>1172–1207</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12717,12 +12717,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1164–1166</t>
+          <t>1208–1209</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 4</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12752,17 +12752,17 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>نعم — راجع تقرير التكرارات</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 4</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>يحتاج مراجعة بشرية</t>
+          <t>ضمن النطاق الواضح</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1167–1169</t>
+          <t>1210–1212</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 6</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12831,12 +12831,12 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>نعم — راجع تقرير التكرارات</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 6</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>1170–1171</t>
+          <t>1213–1214</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1172–1264</t>
+          <t>1215–1307</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1265–1357</t>
+          <t>1308–1400</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1358–1362</t>
+          <t>1401–1405</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1363–1439</t>
+          <t>1406–1482</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1440–1456</t>
+          <t>1483–1499</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1457–1459</t>
+          <t>1500–1502</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1460–1460</t>
+          <t>1503–1503</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1461–1462</t>
+          <t>1504–1505</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>1463–1467</t>
+          <t>1506–1510</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1468–1470</t>
+          <t>1511–1513</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1471–1547</t>
+          <t>1514–1590</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1548–1548</t>
+          <t>1591–1591</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1549–1549</t>
+          <t>1592–1592</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1550–1550</t>
+          <t>1593–1593</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>يحتاج مراجعة بشرية</t>
+          <t>ضمن النطاق الواضح</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1551–1551</t>
+          <t>1594–1594</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1552–1627</t>
+          <t>1595–1670</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1628–1704</t>
+          <t>1671–1747</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1705–1713</t>
+          <t>1748–1756</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1714–1715</t>
+          <t>1757–1758</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1716–1716</t>
+          <t>1759–1759</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -14606,12 +14606,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1717–1718</t>
+          <t>1760–1760</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1719–1794</t>
+          <t>1761–1836</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1795–1800</t>
+          <t>1837–1842</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1801–1801</t>
+          <t>1843–1843</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>مستخرج آلياً؛ تشوّه: فُتات أسطر: 8</t>
+          <t>مستخرج آلياً</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>فُتات أسطر: 8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1802–1802</t>
+          <t>1844–1844</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1803–1803</t>
+          <t>1845–1845</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1804–1804</t>
+          <t>1846–1846</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 1</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>يحتاج مراجعة بشرية</t>
+          <t>ضمن النطاق الواضح</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1805–1805</t>
+          <t>1847–1847</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1806–1811</t>
+          <t>1848–1853</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1812–1887</t>
+          <t>1854–1929</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1888–1891</t>
+          <t>1930–1933</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1892–1894</t>
+          <t>1934–1936</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1895–1895</t>
+          <t>1937–1937</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1896–1953</t>
+          <t>1938–1995</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1954–1958</t>
+          <t>1996–2000</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>1959–1959</t>
+          <t>2001–2001</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1960–1962</t>
+          <t>2002–2004</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1963–2051</t>
+          <t>2005–2093</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2052–2053</t>
+          <t>2094–2095</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2054–2054</t>
+          <t>2096–2096</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2055–2093</t>
+          <t>2097–2135</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2094–2103</t>
+          <t>2136–2145</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2104–2108</t>
+          <t>2146–2150</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">

--- a/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
+++ b/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
@@ -1441,12 +1441,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>محكمة الاستئناف</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>غير متاح</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2508,12 +2508,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>وزارة العدل</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2591,7 +2591,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>وزارة العدل</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5942,22 +5942,22 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>المحكمة التجارية بجدة</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>404–404</t>
+          <t>404–440</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 10، فُتات أسطر: 21</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 10؛ فُتات أسطر: 21</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>405–406</t>
+          <t>441–442</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6104,22 +6104,22 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>محكمة الاستئناف</t>
+          <t>المحكمة العليا</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>407–407</t>
+          <t>443–535</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>مستخرج آلياً</t>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 70، فُتات أسطر: 55</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تكرار حروف: 70؛ فُتات أسطر: 55</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6187,12 +6187,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>محكمة الاستئناف</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>408–418</t>
+          <t>536–546</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>419–419</t>
+          <t>547–547</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>420–423</t>
+          <t>548–551</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>424–425</t>
+          <t>552–553</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>426–431</t>
+          <t>554–559</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>432–437</t>
+          <t>560–565</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>438–440</t>
+          <t>566–568</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>441–442</t>
+          <t>569–570</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>443–444</t>
+          <t>571–572</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>445–448</t>
+          <t>573–576</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>449–455</t>
+          <t>577–583</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>456–459</t>
+          <t>584–587</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>460–461</t>
+          <t>588–589</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>462–463</t>
+          <t>590–591</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>464–465</t>
+          <t>592–593</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>466–502</t>
+          <t>594–630</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>503–507</t>
+          <t>631–635</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7594,12 +7594,12 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>محكمة الاستئناف</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>508–518</t>
+          <t>636–646</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>519–522</t>
+          <t>647–650</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>523–530</t>
+          <t>651–658</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>531–536</t>
+          <t>659–664</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>537–542</t>
+          <t>665–670</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>543–544</t>
+          <t>671–672</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>545–546</t>
+          <t>673–674</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>547–551</t>
+          <t>675–679</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>552–553</t>
+          <t>680–681</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>554–555</t>
+          <t>682–683</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>556–558</t>
+          <t>684–686</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>559–561</t>
+          <t>687–689</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>562–564</t>
+          <t>690–692</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>565–567</t>
+          <t>693–695</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>568–570</t>
+          <t>696–698</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>571–573</t>
+          <t>699–701</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>574–576</t>
+          <t>702–704</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>577–579</t>
+          <t>705–707</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>580–582</t>
+          <t>708–710</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>583–585</t>
+          <t>711–713</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>586–589</t>
+          <t>714–717</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>590–593</t>
+          <t>718–721</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>594–598</t>
+          <t>722–726</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>599–603</t>
+          <t>727–731</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>604–605</t>
+          <t>732–733</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>606–616</t>
+          <t>734–744</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>617–630</t>
+          <t>745–758</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>631–636</t>
+          <t>759–764</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>637–639</t>
+          <t>765–767</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>640–645</t>
+          <t>768–773</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>646–646</t>
+          <t>774–774</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>647–649</t>
+          <t>775–777</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>650–650</t>
+          <t>778–778</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>651–652</t>
+          <t>779–780</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>653–658</t>
+          <t>781–786</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>659–659</t>
+          <t>787–787</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>660–660</t>
+          <t>788–788</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>661–661</t>
+          <t>789–789</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>662–662</t>
+          <t>790–790</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>663–713</t>
+          <t>791–841</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>714–747</t>
+          <t>842–875</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>748–787</t>
+          <t>876–915</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>788–811</t>
+          <t>916–939</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>812–916</t>
+          <t>940–1044</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>917–917</t>
+          <t>1045–1045</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>918–918</t>
+          <t>1046–1046</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>919–935</t>
+          <t>1047–1063</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>936–947</t>
+          <t>1064–1075</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>948–959</t>
+          <t>1076–1087</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>960–967</t>
+          <t>1088–1095</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>968–995</t>
+          <t>1096–1123</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>996–996</t>
+          <t>1124–1124</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>997–997</t>
+          <t>1125–1125</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>998–1015</t>
+          <t>1126–1143</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1016–1020</t>
+          <t>1144–1148</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1021–1029</t>
+          <t>1149–1157</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1030–1031</t>
+          <t>1158–1159</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12213,11 +12213,7 @@
           <t>صورة تقديم الشكوى</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>1445/04/30</t>
-        </is>
-      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
@@ -12236,7 +12232,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1032–1032</t>
+          <t>1160–1160</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12319,7 +12315,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1033–1125</t>
+          <t>1161–1253</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -12402,7 +12398,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1126–1127</t>
+          <t>1254–1255</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -12485,7 +12481,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1128–1136</t>
+          <t>1256–1264</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -12564,7 +12560,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1137–1171</t>
+          <t>1265–1299</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -12643,7 +12639,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1172–1207</t>
+          <t>1300–1335</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12703,7 +12699,11 @@
           <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>08/04/1445</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1208–1209</t>
+          <t>1336–1337</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -12782,7 +12782,11 @@
           <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>16/03/1445</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
@@ -12801,7 +12805,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1210–1212</t>
+          <t>1338–1340</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12880,7 +12884,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>1213–1214</t>
+          <t>1341–1342</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -12963,7 +12967,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1215–1307</t>
+          <t>1343–1435</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13046,7 +13050,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1308–1400</t>
+          <t>1436–1528</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13129,7 +13133,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1401–1405</t>
+          <t>1529–1533</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13212,7 +13216,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1406–1482</t>
+          <t>1534–1610</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13295,7 +13299,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1483–1499</t>
+          <t>1611–1627</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -13378,7 +13382,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1500–1502</t>
+          <t>1628–1630</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -13461,7 +13465,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1503–1503</t>
+          <t>1631–1631</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -13544,7 +13548,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1504–1505</t>
+          <t>1632–1633</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -13627,7 +13631,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>1506–1510</t>
+          <t>1634–1638</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -13710,7 +13714,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1511–1513</t>
+          <t>1639–1641</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -13793,7 +13797,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1514–1590</t>
+          <t>1642–1718</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -13876,7 +13880,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1591–1591</t>
+          <t>1719–1719</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -13959,7 +13963,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1592–1592</t>
+          <t>1720–1720</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14032,7 +14036,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>غير متاح</t>
+          <t>أسامة زيني</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -14042,7 +14046,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1593–1593</t>
+          <t>1721–1721</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -14121,7 +14125,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1594–1594</t>
+          <t>1722–1722</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -14204,7 +14208,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1595–1670</t>
+          <t>1723–1798</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -14287,7 +14291,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1671–1747</t>
+          <t>1799–1875</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -14370,7 +14374,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1748–1756</t>
+          <t>1876–1884</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -14453,7 +14457,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1757–1758</t>
+          <t>1885–1886</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -14532,7 +14536,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1759–1759</t>
+          <t>1887–1887</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -14611,7 +14615,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1760–1760</t>
+          <t>1888–1888</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -14694,7 +14698,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1761–1836</t>
+          <t>1889–1964</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -14777,7 +14781,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1837–1842</t>
+          <t>1965–1970</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -14837,7 +14841,11 @@
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>25/12/1442</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
@@ -14856,7 +14864,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1843–1843</t>
+          <t>1971–1971</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -14916,11 +14924,7 @@
           <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>1445/01/01</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
@@ -14939,7 +14943,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1844–1844</t>
+          <t>1972–1972</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -14999,11 +15003,7 @@
           <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1445/01/01</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>غير متاح</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1845–1845</t>
+          <t>1973–1973</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>غير متاح</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1846–1846</t>
+          <t>1974–1974</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1847–1847</t>
+          <t>1975–1975</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1848–1853</t>
+          <t>1976–1981</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1854–1929</t>
+          <t>1982–2057</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1930–1933</t>
+          <t>2058–2061</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1934–1936</t>
+          <t>2062–2064</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1937–1937</t>
+          <t>2065–2065</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1938–1995</t>
+          <t>2066–2123</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1996–2000</t>
+          <t>2124–2128</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2001–2001</t>
+          <t>2129–2129</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2002–2004</t>
+          <t>2130–2132</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2005–2093</t>
+          <t>2133–2221</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2094–2095</t>
+          <t>2222–2223</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2096–2096</t>
+          <t>2224–2224</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2097–2135</t>
+          <t>2225–2263</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2136–2145</t>
+          <t>2264–2273</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2146–2150</t>
+          <t>2274–2278</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">

--- a/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
+++ b/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
@@ -14036,7 +14036,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>غير متاح</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">

--- a/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
+++ b/zaini_case_audit_output/outputs/package/بطاقات_الوثائق.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q196"/>
+  <dimension ref="A1:Q226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16445,6 +16445,2492 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DOC-196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>حكم ابتدائي ضد الشيخ اسامة زيني - القضية - 42824717 - 01-01-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>01-01-1445</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2279–2298</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jYjqC1mznAUSMVpLmwzmomaDlVSpR467/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DOC-197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>صك حكم ابتدائي رفض الالتماس لعدم الاختصاص ـ 42824717 - 01-07-1447 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>01-07-1447</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2299–2300</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1u8PIQBXWD7vyHWLXcMbzJ3i4n63H1QRF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DOC-198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>13-03-1445</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2301–2373</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ub0rCd1CD38iZBRYw2V5GG4Pg2hiT2c5/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>سليم</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 3</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 3</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DOC-199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ملخص حقوق الملكية.pdf</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2374–2393</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NpF7OxPSOAtOh0rGMo2WylHboEmj5J5N/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 14، فُتات أسطر: 19</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 14؛ فُتات أسطر: 19</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DOC-200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 10 يوم 07-07-1443 هـ للدعوى رقم 42824717 تمسك المدعي بالغبن و صورية العقد.pdf</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>07-07-1443</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2394–2396</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MOmCJpbP1JSTPNHDo7wnCpXpJCmuX3Yl/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DOC-201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 27-01-1444 هـ للدعوى رقم 42824717 طلب القاضي اصل عقد البيع.pdf</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>27-01-1444</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2397–2399</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17gaJ8pLqaw55ceLHlYo4312Kt47vmzaz/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DOC-202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 16 يوم 29-12-1443 هـ للدعوى رقم 42824717 الطعن في عقد البيع وطلب اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>29-12-1443</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2400–2403</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1J1tKOvi55-CsxJHUL99CakmRilK10LXL/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DOC-203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 16 بتاريخ 09-11-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>09-11-1443</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2404–2409</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Ac6bRYCL2dmkfh_v6TwzsVlcGMMOwlvJ/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DOC-204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 12 بتاريخ 19-08-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>19-08-1443</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2410–2415</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sk4qkXLdx5ATlnEOZYERD0Mjy39JeOwH/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DOC-205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 19 يوم 22-03-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>22-03-1444</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2416–2418</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ynqHOzxru-xjSzRNx956ClBhtKWA1xa2/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DOC-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 29-12-1443 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>29-12-1443</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2419–2420</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UZMGfPH_sD2Fk1GZtDSccB_lBmlwo5ko/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DOC-207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 1 بتاريخ 03-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>03-01-1443</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>2421–2423</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1yquu2X6WHiF95GawtPgtA-RTDIpc8Mcd/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DOC-208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 00 يوم 20-02-1445 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>20-02-1445</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2424–2437</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1mynWTK4W3_XUslEgUFrpOkq5czgTTYQo/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 2</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 2</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>DOC-209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 22 يوم 03-06-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>03-06-1444</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2438–2440</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Uz_CI6u1W9CLu6Z9YZ_OuvdddvOEXfTO/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1، فُتات أسطر: 6</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 1؛ فُتات أسطر: 6</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DOC-210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 10 بتاريخ 07-07-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>07-07-1443</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2441–2443</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Bu14__JQQSF88My_C3AIpcOkLktFDf0A/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DOC-211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 9 بتاريخ 29-06-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>29-06-1443</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2444–2445</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1dbdEHHry2SYyZi_v8ChUrsomGSkgKMLK/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DOC-212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 11 بتاريخ 28-07-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>28-07-1443</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2446–2448</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rxJLq40p-JLw31vU0MDQVzebO-G01oMS/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>DOC-213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 8 بتاريخ 17-05-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>17-05-1443</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>2449–2451</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1IDmNeN429NCQRSIGUAQHKJ-aznGuCGys/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DOC-214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 13 بتاريخ 16-10-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>16-10-1443</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2452–2454</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11FQ1ua0n93eUOIGZ2c8QYmDbqKPfQ_jD/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DOC-215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 6 بتاريخ 04-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>04-04-1443</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2455–2456</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16VrbfwMxRHLTE3K2RZk-UFkRCT6zt7dy/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>DOC-216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 15 بتاريخ 02-11-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>02-11-1443</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2457–2459</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1hkfSLIlt1CV7iXSojoDV0DWUdUQ3nhJT/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DOC-217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 20 يوم 21-04-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>21-04-1444</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2460–2462</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1o3gbUf0T-0k2DHnixUjli_gFM_5BHkmF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DOC-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 4 بتاريخ 28-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>28-02-1443</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2463–2465</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1kYpVfNZKMHIfJHFa1GvKldMqUh4NGIQF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DOC-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 2 بتاريخ 23-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>23-01-1443</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2466–2467</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12ZykSkxkU8VZrPR9gtE4xMMtEwcOUWA6/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DOC-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 5 بتاريخ 20-03-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>20-03-1443</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2468–2470</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ptMLbcnKqHkbp9bFlL_QuU5BhxDmjPuf/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DOC-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 23 يوم 02-07-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>02-07-1444</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2471–2473</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1oQqKZgSZmKIfUnGRF0wsCgAmmsrTIUTa/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DOC-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 7 بتاريخ 25-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>25-04-1443</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2474–2475</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UTTWQULs4OBCTZg1QhJl6uak0M6Vl4zT/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>نعم — راجع تقرير التكرارات</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DOC-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 3 بتاريخ 14-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>14-02-1443</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2476–2478</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1n6jZBX4UajjoaQUh0kN6PlwyW2-OTr7Z/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>DOC-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 21 يوم 22-05-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>22-05-1444</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2479–2480</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1a67bUpgWMWC15VqA7HwgLZdu0nCdBupB/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 1</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>DOC-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 14 بتاريخ 25-10-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>25-10-1443</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2481–2484</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1F8edXbcjfBZ928RxuFgI3K-hRcjJnxmC/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>غير متاح</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>مستخرج آلياً؛ تشوّه: تكرار حروف: 3</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>يُراجع الأصل</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>غير محدّد</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>تكرار حروف: 3</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة بشرية</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
